--- a/artfynd/A 6933-2023 artfynd.xlsx
+++ b/artfynd/A 6933-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6933-2023 artfynd.xlsx
+++ b/artfynd/A 6933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105269556</v>
+        <v>111782529</v>
       </c>
       <c r="B2" t="n">
-        <v>9073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101595</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspstumpbagge</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platysoma deplanatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,37 +710,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granhult, Knorrebo, Läckeby, Sm</t>
+          <t>Granhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572370.0938890788</v>
+        <v>572410</v>
       </c>
       <c r="R2" t="n">
-        <v>6300393.215202058</v>
+        <v>6300350</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>U bark på asplåga vid hygge</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,21 +765,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>HLt220715</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -831,53 +781,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110031398</v>
+        <v>111782531</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trakten kring Ebbegärde, Sm</t>
+          <t>Granhult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572299.9299905848</v>
+        <v>572405</v>
       </c>
       <c r="R3" t="n">
-        <v>6300488.276770563</v>
+        <v>6300359</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,49 +880,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Malmqvist</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111782529</v>
+        <v>111782537</v>
       </c>
       <c r="B4" t="n">
-        <v>88869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +927,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572411</v>
+        <v>572143</v>
       </c>
       <c r="R4" t="n">
-        <v>6300350</v>
+        <v>6300253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,15 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111782537</v>
+        <v>111782536</v>
       </c>
       <c r="B5" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,31 +1009,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1103,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572144</v>
+        <v>572185</v>
       </c>
       <c r="R5" t="n">
-        <v>6300253</v>
+        <v>6300110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,62 +1104,68 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111782531</v>
+        <v>105269554</v>
       </c>
       <c r="B6" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>101595</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Aspstumpbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Platysoma deplanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyllenhal, 1808)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granhult, Sm</t>
+          <t>Granhult, Knorrebo, Läckeby, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572405</v>
+        <v>572371</v>
       </c>
       <c r="R6" t="n">
-        <v>6300360</v>
+        <v>6300393</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,17 +1189,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>U bark på asplåga vid hygge</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1210,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>HLt220717</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1278,6 +1238,311 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110031396</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trakten kring Ebbegärde, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572259</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6300484</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110031398</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trakten kring Ebbegärde, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572300</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6300489</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Malmqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111782527</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572302</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6300516</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 blom och 5 rosetter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6933-2023 artfynd.xlsx
+++ b/artfynd/A 6933-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782531</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782536</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105269554</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110031396</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110031398</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,8 +1583,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111782527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>